--- a/data/pmi.xlsx
+++ b/data/pmi.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C62"/>
+  <dimension ref="A1:C63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.5703125" customWidth="1" min="1" max="1"/>
@@ -456,11 +456,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>47</v>
+        <v>56.3</v>
       </c>
       <c r="C2">
         <f>(B2/B14-1)*100</f>
@@ -470,11 +470,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>43.3</v>
+        <v>47</v>
       </c>
       <c r="C3">
         <f>(B3/B15-1)*100</f>
@@ -484,11 +484,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.5</v>
+        <v>43.3</v>
       </c>
       <c r="C4">
         <f>(B4/B16-1)*100</f>
@@ -498,11 +498,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>51.7</v>
+        <v>44.5</v>
       </c>
       <c r="C5">
         <f>(B5/B17-1)*100</f>
@@ -512,11 +512,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>61.6</v>
+        <v>51.7</v>
       </c>
       <c r="C6">
         <f>(B6/B18-1)*100</f>
@@ -526,11 +526,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>50</v>
+        <v>61.6</v>
       </c>
       <c r="C7">
         <f>(B7/B19-1)*100</f>
@@ -540,11 +540,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>54.6</v>
+        <v>50</v>
       </c>
       <c r="C8">
         <f>(B8/B20-1)*100</f>
@@ -554,7 +554,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -568,11 +568,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>53.8</v>
+        <v>54.6</v>
       </c>
       <c r="C10">
         <f>(B10/B22-1)*100</f>
@@ -582,11 +582,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>55.6</v>
+        <v>53.8</v>
       </c>
       <c r="C11">
         <f>(B11/B23-1)*100</f>
@@ -596,11 +596,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>53.6</v>
+        <v>55.6</v>
       </c>
       <c r="C12">
         <f>(B12/B24-1)*100</f>
@@ -608,11 +608,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>45627</v>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>44.3</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>53.6</v>
       </c>
       <c r="C13">
         <f>(B13/B25-1)*100</f>
@@ -620,23 +622,23 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n">
+      <c r="A14" s="2" t="n">
+        <v>45627</v>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="C14">
+        <f>(B14/B26-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
         <v>45597</v>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B15" s="3" t="n">
         <v>49.7</v>
-      </c>
-      <c r="C14" s="1">
-        <f>(B14/B26-1)*100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>45566</v>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>52.2</v>
       </c>
       <c r="C15" s="1">
         <f>(B15/B27-1)*100</f>
@@ -644,11 +646,11 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n">
-        <v>45536</v>
+      <c r="A16" s="2" t="n">
+        <v>45566</v>
       </c>
       <c r="B16" s="3" t="n">
-        <v>54.5</v>
+        <v>52.2</v>
       </c>
       <c r="C16" s="1">
         <f>(B16/B28-1)*100</f>
@@ -656,11 +658,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>45505</v>
+      <c r="A17" s="4" t="n">
+        <v>45536</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>50.3</v>
+        <v>54.5</v>
       </c>
       <c r="C17" s="1">
         <f>(B17/B29-1)*100</f>
@@ -668,11 +670,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n">
-        <v>45474</v>
+      <c r="A18" s="2" t="n">
+        <v>45505</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v>55.3</v>
+        <v>50.3</v>
       </c>
       <c r="C18" s="1">
         <f>(B18/B30-1)*100</f>
@@ -680,11 +682,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>45444</v>
+      <c r="A19" s="4" t="n">
+        <v>45474</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>62.4</v>
+        <v>55.3</v>
       </c>
       <c r="C19" s="1">
         <f>(B19/B31-1)*100</f>
@@ -692,11 +694,11 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n">
-        <v>45413</v>
+      <c r="A20" s="2" t="n">
+        <v>45444</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v>59.1</v>
+        <v>62.4</v>
       </c>
       <c r="C20" s="1">
         <f>(B20/B32-1)*100</f>
@@ -704,11 +706,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>45383</v>
+      <c r="A21" s="4" t="n">
+        <v>45413</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>65.7</v>
+        <v>59.1</v>
       </c>
       <c r="C21" s="1">
         <f>(B21/B33-1)*100</f>
@@ -716,11 +718,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="n">
-        <v>45352</v>
+      <c r="A22" s="2" t="n">
+        <v>45383</v>
       </c>
       <c r="B22" s="3" t="n">
-        <v>63</v>
+        <v>65.7</v>
       </c>
       <c r="C22" s="1">
         <f>(B22/B34-1)*100</f>
@@ -728,11 +730,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>45323</v>
+      <c r="A23" s="4" t="n">
+        <v>45352</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>56.3</v>
+        <v>63</v>
       </c>
       <c r="C23" s="1">
         <f>(B23/B35-1)*100</f>
@@ -740,11 +742,11 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="n">
-        <v>45292</v>
+      <c r="A24" s="2" t="n">
+        <v>45323</v>
       </c>
       <c r="B24" s="3" t="n">
-        <v>54.4</v>
+        <v>56.3</v>
       </c>
       <c r="C24" s="1">
         <f>(B24/B36-1)*100</f>
@@ -752,11 +754,11 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>45261</v>
+      <c r="A25" s="4" t="n">
+        <v>45292</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>43.7</v>
+        <v>54.4</v>
       </c>
       <c r="C25" s="1">
         <f>(B25/B37-1)*100</f>
@@ -764,11 +766,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="n">
-        <v>45231</v>
+      <c r="A26" s="2" t="n">
+        <v>45261</v>
       </c>
       <c r="B26" s="3" t="n">
-        <v>54.7</v>
+        <v>43.7</v>
       </c>
       <c r="C26" s="1">
         <f>(B26/B38-1)*100</f>
@@ -776,11 +778,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>45200</v>
+      <c r="A27" s="4" t="n">
+        <v>45231</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>53.4</v>
+        <v>54.7</v>
       </c>
       <c r="C27" s="1">
         <f>(B27/B39-1)*100</f>
@@ -788,11 +790,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="n">
-        <v>45170</v>
+      <c r="A28" s="2" t="n">
+        <v>45200</v>
       </c>
       <c r="B28" s="3" t="n">
-        <v>53.1</v>
+        <v>53.4</v>
       </c>
       <c r="C28" s="1">
         <f>(B28/B40-1)*100</f>
@@ -800,11 +802,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>45139</v>
+      <c r="A29" s="4" t="n">
+        <v>45170</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>53.5</v>
+        <v>53.1</v>
       </c>
       <c r="C29" s="1">
         <f>(B29/B41-1)*100</f>
@@ -812,11 +814,11 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="n">
-        <v>45108</v>
+      <c r="A30" s="2" t="n">
+        <v>45139</v>
       </c>
       <c r="B30" s="3" t="n">
-        <v>48.6</v>
+        <v>53.5</v>
       </c>
       <c r="C30" s="1">
         <f>(B30/B42-1)*100</f>
@@ -824,11 +826,11 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>45078</v>
+      <c r="A31" s="4" t="n">
+        <v>45108</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>50.2</v>
+        <v>48.6</v>
       </c>
       <c r="C31" s="1">
         <f>(B31/B43-1)*100</f>
@@ -836,11 +838,11 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="n">
-        <v>45047</v>
+      <c r="A32" s="2" t="n">
+        <v>45078</v>
       </c>
       <c r="B32" s="3" t="n">
-        <v>53.5</v>
+        <v>50.2</v>
       </c>
       <c r="C32" s="1">
         <f>(B32/B44-1)*100</f>
@@ -848,11 +850,11 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>45017</v>
+      <c r="A33" s="4" t="n">
+        <v>45047</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>56.8</v>
+        <v>53.5</v>
       </c>
       <c r="C33" s="1">
         <f>(B33/B45-1)*100</f>
@@ -860,11 +862,11 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="n">
-        <v>44986</v>
+      <c r="A34" s="2" t="n">
+        <v>45017</v>
       </c>
       <c r="B34" s="3" t="n">
-        <v>58.2</v>
+        <v>56.8</v>
       </c>
       <c r="C34" s="1">
         <f>(B34/B46-1)*100</f>
@@ -872,11 +874,11 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
-        <v>44958</v>
+      <c r="A35" s="4" t="n">
+        <v>44986</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>51.6</v>
+        <v>58.2</v>
       </c>
       <c r="C35" s="1">
         <f>(B35/B47-1)*100</f>
@@ -884,11 +886,11 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="n">
-        <v>44927</v>
+      <c r="A36" s="2" t="n">
+        <v>44958</v>
       </c>
       <c r="B36" s="3" t="n">
-        <v>60.1</v>
+        <v>51.6</v>
       </c>
       <c r="C36" s="1">
         <f>(B36/B48-1)*100</f>
@@ -896,11 +898,11 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>44896</v>
+      <c r="A37" s="4" t="n">
+        <v>44927</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>49.3</v>
+        <v>60.1</v>
       </c>
       <c r="C37" s="1">
         <f>(B37/B49-1)*100</f>
@@ -908,11 +910,11 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="n">
-        <v>44866</v>
+      <c r="A38" s="2" t="n">
+        <v>44896</v>
       </c>
       <c r="B38" s="3" t="n">
-        <v>51.5</v>
+        <v>49.3</v>
       </c>
       <c r="C38" s="1">
         <f>(B38/B50-1)*100</f>
@@ -920,11 +922,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
-        <v>44835</v>
+      <c r="A39" s="4" t="n">
+        <v>44866</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>52.8</v>
+        <v>51.5</v>
       </c>
       <c r="C39" s="1">
         <f>(B39/B51-1)*100</f>
@@ -932,11 +934,11 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="n">
-        <v>44805</v>
+      <c r="A40" s="2" t="n">
+        <v>44835</v>
       </c>
       <c r="B40" s="3" t="n">
-        <v>52.6</v>
+        <v>52.8</v>
       </c>
       <c r="C40" s="1">
         <f>(B40/B52-1)*100</f>
@@ -944,11 +946,11 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
-        <v>44774</v>
+      <c r="A41" s="4" t="n">
+        <v>44805</v>
       </c>
       <c r="B41" s="3" t="n">
-        <v>53.5</v>
+        <v>52.6</v>
       </c>
       <c r="C41" s="1">
         <f>(B41/B53-1)*100</f>
@@ -956,11 +958,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="n">
-        <v>44743</v>
+      <c r="A42" s="2" t="n">
+        <v>44774</v>
       </c>
       <c r="B42" s="3" t="n">
-        <v>57</v>
+        <v>53.5</v>
       </c>
       <c r="C42" s="1">
         <f>(B42/B54-1)*100</f>
@@ -968,11 +970,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
-        <v>44713</v>
+      <c r="A43" s="4" t="n">
+        <v>44743</v>
       </c>
       <c r="B43" s="3" t="n">
-        <v>53.8</v>
+        <v>57</v>
       </c>
       <c r="C43" s="1">
         <f>(B43/B55-1)*100</f>
@@ -980,11 +982,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="n">
-        <v>44682</v>
+      <c r="A44" s="2" t="n">
+        <v>44713</v>
       </c>
       <c r="B44" s="3" t="n">
-        <v>61.9</v>
+        <v>53.8</v>
       </c>
       <c r="C44" s="1">
         <f>(B44/B56-1)*100</f>
@@ -992,11 +994,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
-        <v>44652</v>
+      <c r="A45" s="4" t="n">
+        <v>44682</v>
       </c>
       <c r="B45" s="3" t="n">
-        <v>69.90000000000001</v>
+        <v>61.9</v>
       </c>
       <c r="C45" s="1">
         <f>(B45/B57-1)*100</f>
@@ -1004,11 +1006,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="n">
-        <v>44621</v>
+      <c r="A46" s="2" t="n">
+        <v>44652</v>
       </c>
       <c r="B46" s="3" t="n">
-        <v>63</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="C46" s="1">
         <f>(B46/B58-1)*100</f>
@@ -1016,11 +1018,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
-        <v>44593</v>
+      <c r="A47" s="4" t="n">
+        <v>44621</v>
       </c>
       <c r="B47" s="3" t="n">
-        <v>63.9</v>
+        <v>63</v>
       </c>
       <c r="C47" s="1">
         <f>(B47/B59-1)*100</f>
@@ -1028,11 +1030,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="n">
-        <v>44562</v>
+      <c r="A48" s="2" t="n">
+        <v>44593</v>
       </c>
       <c r="B48" s="3" t="n">
-        <v>64.90000000000001</v>
+        <v>63.9</v>
       </c>
       <c r="C48" s="1">
         <f>(B48/B60-1)*100</f>
@@ -1040,11 +1042,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
-        <v>44531</v>
+      <c r="A49" s="4" t="n">
+        <v>44562</v>
       </c>
       <c r="B49" s="3" t="n">
-        <v>58.1</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="C49" s="1">
         <f>(B49/B61-1)*100</f>
@@ -1052,23 +1054,23 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="n">
+      <c r="A50" s="2" t="n">
+        <v>44531</v>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="C50" s="1">
+        <f>(B50/B62-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="n">
         <v>44501</v>
       </c>
-      <c r="B50" s="3" t="n">
+      <c r="B51" s="3" t="n">
         <v>61.2</v>
-      </c>
-      <c r="C50">
-        <f>(B50/B62-1)*100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="n">
-        <v>44470</v>
-      </c>
-      <c r="B51" s="3" t="n">
-        <v>63.2</v>
       </c>
       <c r="C51">
         <f>(B51/B63-1)*100</f>
@@ -1076,11 +1078,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="n">
-        <v>44440</v>
+      <c r="A52" s="2" t="n">
+        <v>44470</v>
       </c>
       <c r="B52" s="3" t="n">
-        <v>59.1</v>
+        <v>63.2</v>
       </c>
       <c r="C52">
         <f>(B52/B64-1)*100</f>
@@ -1088,11 +1090,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
-        <v>44409</v>
+      <c r="A53" s="4" t="n">
+        <v>44440</v>
       </c>
       <c r="B53" s="3" t="n">
-        <v>61.6</v>
+        <v>59.1</v>
       </c>
       <c r="C53">
         <f>(B53/B65-1)*100</f>
@@ -1100,11 +1102,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="n">
-        <v>44378</v>
+      <c r="A54" s="2" t="n">
+        <v>44409</v>
       </c>
       <c r="B54" s="3" t="n">
-        <v>63.4</v>
+        <v>61.6</v>
       </c>
       <c r="C54">
         <f>(B54/B66-1)*100</f>
@@ -1112,11 +1114,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
-        <v>44348</v>
+      <c r="A55" s="4" t="n">
+        <v>44378</v>
       </c>
       <c r="B55" s="3" t="n">
-        <v>63.8</v>
+        <v>63.4</v>
       </c>
       <c r="C55">
         <f>(B55/B67-1)*100</f>
@@ -1124,11 +1126,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="n">
-        <v>44317</v>
+      <c r="A56" s="2" t="n">
+        <v>44348</v>
       </c>
       <c r="B56" s="3" t="n">
-        <v>55.2</v>
+        <v>63.8</v>
       </c>
       <c r="C56">
         <f>(B56/B68-1)*100</f>
@@ -1136,11 +1138,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
-        <v>44287</v>
+      <c r="A57" s="4" t="n">
+        <v>44317</v>
       </c>
       <c r="B57" s="3" t="n">
-        <v>59.3</v>
+        <v>55.2</v>
       </c>
       <c r="C57">
         <f>(B57/B69-1)*100</f>
@@ -1148,11 +1150,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="n">
-        <v>44256</v>
+      <c r="A58" s="2" t="n">
+        <v>44287</v>
       </c>
       <c r="B58" s="3" t="n">
-        <v>62.1</v>
+        <v>59.3</v>
       </c>
       <c r="C58">
         <f>(B58/B70-1)*100</f>
@@ -1160,11 +1162,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
-        <v>44228</v>
+      <c r="A59" s="4" t="n">
+        <v>44256</v>
       </c>
       <c r="B59" s="3" t="n">
-        <v>66.40000000000001</v>
+        <v>62.1</v>
       </c>
       <c r="C59">
         <f>(B59/B71-1)*100</f>
@@ -1172,11 +1174,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="n">
-        <v>44197</v>
+      <c r="A60" s="2" t="n">
+        <v>44228</v>
       </c>
       <c r="B60" s="3" t="n">
-        <v>48.4</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="C60">
         <f>(B60/B72-1)*100</f>
@@ -1184,11 +1186,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
-        <v>44166</v>
+      <c r="A61" s="4" t="n">
+        <v>44197</v>
       </c>
       <c r="B61" s="3" t="n">
-        <v>46.7</v>
+        <v>48.4</v>
       </c>
       <c r="C61">
         <f>(B61/B73-1)*100</f>
@@ -1196,14 +1198,26 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="n">
-        <v>44136</v>
+      <c r="A62" s="2" t="n">
+        <v>44166</v>
       </c>
       <c r="B62" s="3" t="n">
-        <v>52.7</v>
+        <v>46.7</v>
       </c>
       <c r="C62">
         <f>(B62/B74-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>44136</v>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="C63">
+        <f>(B63/B75-1)*100</f>
         <v/>
       </c>
     </row>

--- a/data/pmi.xlsx
+++ b/data/pmi.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C63"/>
+  <dimension ref="A1:C64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.5703125" customWidth="1" min="1" max="1"/>
@@ -456,11 +456,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>56.3</v>
+        <v>56.5</v>
       </c>
       <c r="C2">
         <f>(B2/B14-1)*100</f>
@@ -470,11 +470,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>47</v>
+        <v>56.3</v>
       </c>
       <c r="C3">
         <f>(B3/B15-1)*100</f>
@@ -484,11 +484,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>43.3</v>
+        <v>47</v>
       </c>
       <c r="C4">
         <f>(B4/B16-1)*100</f>
@@ -498,11 +498,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>44.5</v>
+        <v>43.3</v>
       </c>
       <c r="C5">
         <f>(B5/B17-1)*100</f>
@@ -512,11 +512,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>51.7</v>
+        <v>44.5</v>
       </c>
       <c r="C6">
         <f>(B6/B18-1)*100</f>
@@ -526,11 +526,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>61.6</v>
+        <v>51.7</v>
       </c>
       <c r="C7">
         <f>(B7/B19-1)*100</f>
@@ -540,11 +540,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>61.6</v>
       </c>
       <c r="C8">
         <f>(B8/B20-1)*100</f>
@@ -554,11 +554,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>54.6</v>
+        <v>50</v>
       </c>
       <c r="C9">
         <f>(B9/B21-1)*100</f>
@@ -568,7 +568,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -582,11 +582,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>53.8</v>
+        <v>54.6</v>
       </c>
       <c r="C11">
         <f>(B11/B23-1)*100</f>
@@ -596,11 +596,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>55.6</v>
+        <v>53.8</v>
       </c>
       <c r="C12">
         <f>(B12/B24-1)*100</f>
@@ -610,11 +610,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>53.6</v>
+        <v>55.6</v>
       </c>
       <c r="C13">
         <f>(B13/B25-1)*100</f>
@@ -622,11 +622,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>45627</v>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>44.3</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>53.6</v>
       </c>
       <c r="C14">
         <f>(B14/B26-1)*100</f>
@@ -634,23 +636,23 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
+      <c r="A15" s="2" t="n">
+        <v>45627</v>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="C15">
+        <f>(B15/B27-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
         <v>45597</v>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B16" s="3" t="n">
         <v>49.7</v>
-      </c>
-      <c r="C15" s="1">
-        <f>(B15/B27-1)*100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>45566</v>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>52.2</v>
       </c>
       <c r="C16" s="1">
         <f>(B16/B28-1)*100</f>
@@ -658,11 +660,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
-        <v>45536</v>
+      <c r="A17" s="2" t="n">
+        <v>45566</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>54.5</v>
+        <v>52.2</v>
       </c>
       <c r="C17" s="1">
         <f>(B17/B29-1)*100</f>
@@ -670,11 +672,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>45505</v>
+      <c r="A18" s="4" t="n">
+        <v>45536</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v>50.3</v>
+        <v>54.5</v>
       </c>
       <c r="C18" s="1">
         <f>(B18/B30-1)*100</f>
@@ -682,11 +684,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n">
-        <v>45474</v>
+      <c r="A19" s="2" t="n">
+        <v>45505</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>55.3</v>
+        <v>50.3</v>
       </c>
       <c r="C19" s="1">
         <f>(B19/B31-1)*100</f>
@@ -694,11 +696,11 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>45444</v>
+      <c r="A20" s="4" t="n">
+        <v>45474</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v>62.4</v>
+        <v>55.3</v>
       </c>
       <c r="C20" s="1">
         <f>(B20/B32-1)*100</f>
@@ -706,11 +708,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n">
-        <v>45413</v>
+      <c r="A21" s="2" t="n">
+        <v>45444</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>59.1</v>
+        <v>62.4</v>
       </c>
       <c r="C21" s="1">
         <f>(B21/B33-1)*100</f>
@@ -718,11 +720,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>45383</v>
+      <c r="A22" s="4" t="n">
+        <v>45413</v>
       </c>
       <c r="B22" s="3" t="n">
-        <v>65.7</v>
+        <v>59.1</v>
       </c>
       <c r="C22" s="1">
         <f>(B22/B34-1)*100</f>
@@ -730,11 +732,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n">
-        <v>45352</v>
+      <c r="A23" s="2" t="n">
+        <v>45383</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>63</v>
+        <v>65.7</v>
       </c>
       <c r="C23" s="1">
         <f>(B23/B35-1)*100</f>
@@ -742,11 +744,11 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>45323</v>
+      <c r="A24" s="4" t="n">
+        <v>45352</v>
       </c>
       <c r="B24" s="3" t="n">
-        <v>56.3</v>
+        <v>63</v>
       </c>
       <c r="C24" s="1">
         <f>(B24/B36-1)*100</f>
@@ -754,11 +756,11 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="n">
-        <v>45292</v>
+      <c r="A25" s="2" t="n">
+        <v>45323</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>54.4</v>
+        <v>56.3</v>
       </c>
       <c r="C25" s="1">
         <f>(B25/B37-1)*100</f>
@@ -766,11 +768,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>45261</v>
+      <c r="A26" s="4" t="n">
+        <v>45292</v>
       </c>
       <c r="B26" s="3" t="n">
-        <v>43.7</v>
+        <v>54.4</v>
       </c>
       <c r="C26" s="1">
         <f>(B26/B38-1)*100</f>
@@ -778,11 +780,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="n">
-        <v>45231</v>
+      <c r="A27" s="2" t="n">
+        <v>45261</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>54.7</v>
+        <v>43.7</v>
       </c>
       <c r="C27" s="1">
         <f>(B27/B39-1)*100</f>
@@ -790,11 +792,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>45200</v>
+      <c r="A28" s="4" t="n">
+        <v>45231</v>
       </c>
       <c r="B28" s="3" t="n">
-        <v>53.4</v>
+        <v>54.7</v>
       </c>
       <c r="C28" s="1">
         <f>(B28/B40-1)*100</f>
@@ -802,11 +804,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="n">
-        <v>45170</v>
+      <c r="A29" s="2" t="n">
+        <v>45200</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>53.1</v>
+        <v>53.4</v>
       </c>
       <c r="C29" s="1">
         <f>(B29/B41-1)*100</f>
@@ -814,11 +816,11 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>45139</v>
+      <c r="A30" s="4" t="n">
+        <v>45170</v>
       </c>
       <c r="B30" s="3" t="n">
-        <v>53.5</v>
+        <v>53.1</v>
       </c>
       <c r="C30" s="1">
         <f>(B30/B42-1)*100</f>
@@ -826,11 +828,11 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="n">
-        <v>45108</v>
+      <c r="A31" s="2" t="n">
+        <v>45139</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>48.6</v>
+        <v>53.5</v>
       </c>
       <c r="C31" s="1">
         <f>(B31/B43-1)*100</f>
@@ -838,11 +840,11 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>45078</v>
+      <c r="A32" s="4" t="n">
+        <v>45108</v>
       </c>
       <c r="B32" s="3" t="n">
-        <v>50.2</v>
+        <v>48.6</v>
       </c>
       <c r="C32" s="1">
         <f>(B32/B44-1)*100</f>
@@ -850,11 +852,11 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="n">
-        <v>45047</v>
+      <c r="A33" s="2" t="n">
+        <v>45078</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>53.5</v>
+        <v>50.2</v>
       </c>
       <c r="C33" s="1">
         <f>(B33/B45-1)*100</f>
@@ -862,11 +864,11 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
-        <v>45017</v>
+      <c r="A34" s="4" t="n">
+        <v>45047</v>
       </c>
       <c r="B34" s="3" t="n">
-        <v>56.8</v>
+        <v>53.5</v>
       </c>
       <c r="C34" s="1">
         <f>(B34/B46-1)*100</f>
@@ -874,11 +876,11 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="n">
-        <v>44986</v>
+      <c r="A35" s="2" t="n">
+        <v>45017</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>58.2</v>
+        <v>56.8</v>
       </c>
       <c r="C35" s="1">
         <f>(B35/B47-1)*100</f>
@@ -886,11 +888,11 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
-        <v>44958</v>
+      <c r="A36" s="4" t="n">
+        <v>44986</v>
       </c>
       <c r="B36" s="3" t="n">
-        <v>51.6</v>
+        <v>58.2</v>
       </c>
       <c r="C36" s="1">
         <f>(B36/B48-1)*100</f>
@@ -898,11 +900,11 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="n">
-        <v>44927</v>
+      <c r="A37" s="2" t="n">
+        <v>44958</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>60.1</v>
+        <v>51.6</v>
       </c>
       <c r="C37" s="1">
         <f>(B37/B49-1)*100</f>
@@ -910,11 +912,11 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>44896</v>
+      <c r="A38" s="4" t="n">
+        <v>44927</v>
       </c>
       <c r="B38" s="3" t="n">
-        <v>49.3</v>
+        <v>60.1</v>
       </c>
       <c r="C38" s="1">
         <f>(B38/B50-1)*100</f>
@@ -922,11 +924,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="n">
-        <v>44866</v>
+      <c r="A39" s="2" t="n">
+        <v>44896</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>51.5</v>
+        <v>49.3</v>
       </c>
       <c r="C39" s="1">
         <f>(B39/B51-1)*100</f>
@@ -934,11 +936,11 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
-        <v>44835</v>
+      <c r="A40" s="4" t="n">
+        <v>44866</v>
       </c>
       <c r="B40" s="3" t="n">
-        <v>52.8</v>
+        <v>51.5</v>
       </c>
       <c r="C40" s="1">
         <f>(B40/B52-1)*100</f>
@@ -946,11 +948,11 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="n">
-        <v>44805</v>
+      <c r="A41" s="2" t="n">
+        <v>44835</v>
       </c>
       <c r="B41" s="3" t="n">
-        <v>52.6</v>
+        <v>52.8</v>
       </c>
       <c r="C41" s="1">
         <f>(B41/B53-1)*100</f>
@@ -958,11 +960,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
-        <v>44774</v>
+      <c r="A42" s="4" t="n">
+        <v>44805</v>
       </c>
       <c r="B42" s="3" t="n">
-        <v>53.5</v>
+        <v>52.6</v>
       </c>
       <c r="C42" s="1">
         <f>(B42/B54-1)*100</f>
@@ -970,11 +972,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="n">
-        <v>44743</v>
+      <c r="A43" s="2" t="n">
+        <v>44774</v>
       </c>
       <c r="B43" s="3" t="n">
-        <v>57</v>
+        <v>53.5</v>
       </c>
       <c r="C43" s="1">
         <f>(B43/B55-1)*100</f>
@@ -982,11 +984,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
-        <v>44713</v>
+      <c r="A44" s="4" t="n">
+        <v>44743</v>
       </c>
       <c r="B44" s="3" t="n">
-        <v>53.8</v>
+        <v>57</v>
       </c>
       <c r="C44" s="1">
         <f>(B44/B56-1)*100</f>
@@ -994,11 +996,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="n">
-        <v>44682</v>
+      <c r="A45" s="2" t="n">
+        <v>44713</v>
       </c>
       <c r="B45" s="3" t="n">
-        <v>61.9</v>
+        <v>53.8</v>
       </c>
       <c r="C45" s="1">
         <f>(B45/B57-1)*100</f>
@@ -1006,11 +1008,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
-        <v>44652</v>
+      <c r="A46" s="4" t="n">
+        <v>44682</v>
       </c>
       <c r="B46" s="3" t="n">
-        <v>69.90000000000001</v>
+        <v>61.9</v>
       </c>
       <c r="C46" s="1">
         <f>(B46/B58-1)*100</f>
@@ -1018,11 +1020,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="n">
-        <v>44621</v>
+      <c r="A47" s="2" t="n">
+        <v>44652</v>
       </c>
       <c r="B47" s="3" t="n">
-        <v>63</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="C47" s="1">
         <f>(B47/B59-1)*100</f>
@@ -1030,11 +1032,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
-        <v>44593</v>
+      <c r="A48" s="4" t="n">
+        <v>44621</v>
       </c>
       <c r="B48" s="3" t="n">
-        <v>63.9</v>
+        <v>63</v>
       </c>
       <c r="C48" s="1">
         <f>(B48/B60-1)*100</f>
@@ -1042,11 +1044,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="n">
-        <v>44562</v>
+      <c r="A49" s="2" t="n">
+        <v>44593</v>
       </c>
       <c r="B49" s="3" t="n">
-        <v>64.90000000000001</v>
+        <v>63.9</v>
       </c>
       <c r="C49" s="1">
         <f>(B49/B61-1)*100</f>
@@ -1054,11 +1056,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
-        <v>44531</v>
+      <c r="A50" s="4" t="n">
+        <v>44562</v>
       </c>
       <c r="B50" s="3" t="n">
-        <v>58.1</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="C50" s="1">
         <f>(B50/B62-1)*100</f>
@@ -1066,23 +1068,23 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="n">
+      <c r="A51" s="2" t="n">
+        <v>44531</v>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="C51" s="1">
+        <f>(B51/B63-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
         <v>44501</v>
       </c>
-      <c r="B51" s="3" t="n">
+      <c r="B52" s="3" t="n">
         <v>61.2</v>
-      </c>
-      <c r="C51">
-        <f>(B51/B63-1)*100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="n">
-        <v>44470</v>
-      </c>
-      <c r="B52" s="3" t="n">
-        <v>63.2</v>
       </c>
       <c r="C52">
         <f>(B52/B64-1)*100</f>
@@ -1090,11 +1092,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="n">
-        <v>44440</v>
+      <c r="A53" s="2" t="n">
+        <v>44470</v>
       </c>
       <c r="B53" s="3" t="n">
-        <v>59.1</v>
+        <v>63.2</v>
       </c>
       <c r="C53">
         <f>(B53/B65-1)*100</f>
@@ -1102,11 +1104,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
-        <v>44409</v>
+      <c r="A54" s="4" t="n">
+        <v>44440</v>
       </c>
       <c r="B54" s="3" t="n">
-        <v>61.6</v>
+        <v>59.1</v>
       </c>
       <c r="C54">
         <f>(B54/B66-1)*100</f>
@@ -1114,11 +1116,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="n">
-        <v>44378</v>
+      <c r="A55" s="2" t="n">
+        <v>44409</v>
       </c>
       <c r="B55" s="3" t="n">
-        <v>63.4</v>
+        <v>61.6</v>
       </c>
       <c r="C55">
         <f>(B55/B67-1)*100</f>
@@ -1126,11 +1128,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
-        <v>44348</v>
+      <c r="A56" s="4" t="n">
+        <v>44378</v>
       </c>
       <c r="B56" s="3" t="n">
-        <v>63.8</v>
+        <v>63.4</v>
       </c>
       <c r="C56">
         <f>(B56/B68-1)*100</f>
@@ -1138,11 +1140,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="n">
-        <v>44317</v>
+      <c r="A57" s="2" t="n">
+        <v>44348</v>
       </c>
       <c r="B57" s="3" t="n">
-        <v>55.2</v>
+        <v>63.8</v>
       </c>
       <c r="C57">
         <f>(B57/B69-1)*100</f>
@@ -1150,11 +1152,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
-        <v>44287</v>
+      <c r="A58" s="4" t="n">
+        <v>44317</v>
       </c>
       <c r="B58" s="3" t="n">
-        <v>59.3</v>
+        <v>55.2</v>
       </c>
       <c r="C58">
         <f>(B58/B70-1)*100</f>
@@ -1162,11 +1164,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="n">
-        <v>44256</v>
+      <c r="A59" s="2" t="n">
+        <v>44287</v>
       </c>
       <c r="B59" s="3" t="n">
-        <v>62.1</v>
+        <v>59.3</v>
       </c>
       <c r="C59">
         <f>(B59/B71-1)*100</f>
@@ -1174,11 +1176,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
-        <v>44228</v>
+      <c r="A60" s="4" t="n">
+        <v>44256</v>
       </c>
       <c r="B60" s="3" t="n">
-        <v>66.40000000000001</v>
+        <v>62.1</v>
       </c>
       <c r="C60">
         <f>(B60/B72-1)*100</f>
@@ -1186,11 +1188,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="n">
-        <v>44197</v>
+      <c r="A61" s="2" t="n">
+        <v>44228</v>
       </c>
       <c r="B61" s="3" t="n">
-        <v>48.4</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="C61">
         <f>(B61/B73-1)*100</f>
@@ -1198,11 +1200,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
-        <v>44166</v>
+      <c r="A62" s="4" t="n">
+        <v>44197</v>
       </c>
       <c r="B62" s="3" t="n">
-        <v>46.7</v>
+        <v>48.4</v>
       </c>
       <c r="C62">
         <f>(B62/B74-1)*100</f>
@@ -1210,14 +1212,26 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="n">
-        <v>44136</v>
+      <c r="A63" s="2" t="n">
+        <v>44166</v>
       </c>
       <c r="B63" s="3" t="n">
-        <v>52.7</v>
+        <v>46.7</v>
       </c>
       <c r="C63">
         <f>(B63/B75-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>44136</v>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="C64">
+        <f>(B64/B76-1)*100</f>
         <v/>
       </c>
     </row>

--- a/data/pmi.xlsx
+++ b/data/pmi.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C64"/>
+  <dimension ref="A1:C65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.5703125" customWidth="1" min="1" max="1"/>
@@ -456,11 +456,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>56.5</v>
+        <v>61.3</v>
       </c>
       <c r="C2">
         <f>(B2/B14-1)*100</f>
@@ -470,11 +470,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>56.3</v>
+        <v>56.5</v>
       </c>
       <c r="C3">
         <f>(B3/B15-1)*100</f>
@@ -484,11 +484,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>47</v>
+        <v>56.3</v>
       </c>
       <c r="C4">
         <f>(B4/B16-1)*100</f>
@@ -498,11 +498,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>43.3</v>
+        <v>47</v>
       </c>
       <c r="C5">
         <f>(B5/B17-1)*100</f>
@@ -512,11 +512,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44.5</v>
+        <v>43.3</v>
       </c>
       <c r="C6">
         <f>(B6/B18-1)*100</f>
@@ -526,11 +526,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>51.7</v>
+        <v>44.5</v>
       </c>
       <c r="C7">
         <f>(B7/B19-1)*100</f>
@@ -540,11 +540,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>61.6</v>
+        <v>51.7</v>
       </c>
       <c r="C8">
         <f>(B8/B20-1)*100</f>
@@ -554,11 +554,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>61.6</v>
       </c>
       <c r="C9">
         <f>(B9/B21-1)*100</f>
@@ -568,11 +568,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>54.6</v>
+        <v>50</v>
       </c>
       <c r="C10">
         <f>(B10/B22-1)*100</f>
@@ -582,7 +582,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -596,11 +596,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>53.8</v>
+        <v>54.6</v>
       </c>
       <c r="C12">
         <f>(B12/B24-1)*100</f>
@@ -610,11 +610,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>55.6</v>
+        <v>53.8</v>
       </c>
       <c r="C13">
         <f>(B13/B25-1)*100</f>
@@ -624,11 +624,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>53.6</v>
+        <v>55.6</v>
       </c>
       <c r="C14">
         <f>(B14/B26-1)*100</f>
@@ -636,11 +636,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>45627</v>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>44.3</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>53.6</v>
       </c>
       <c r="C15">
         <f>(B15/B27-1)*100</f>
@@ -648,23 +650,23 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n">
+      <c r="A16" s="2" t="n">
+        <v>45627</v>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="C16">
+        <f>(B16/B28-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
         <v>45597</v>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B17" s="3" t="n">
         <v>49.7</v>
-      </c>
-      <c r="C16" s="1">
-        <f>(B16/B28-1)*100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>45566</v>
-      </c>
-      <c r="B17" s="3" t="n">
-        <v>52.2</v>
       </c>
       <c r="C17" s="1">
         <f>(B17/B29-1)*100</f>
@@ -672,11 +674,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n">
-        <v>45536</v>
+      <c r="A18" s="2" t="n">
+        <v>45566</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v>54.5</v>
+        <v>52.2</v>
       </c>
       <c r="C18" s="1">
         <f>(B18/B30-1)*100</f>
@@ -684,11 +686,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>45505</v>
+      <c r="A19" s="4" t="n">
+        <v>45536</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>50.3</v>
+        <v>54.5</v>
       </c>
       <c r="C19" s="1">
         <f>(B19/B31-1)*100</f>
@@ -696,11 +698,11 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n">
-        <v>45474</v>
+      <c r="A20" s="2" t="n">
+        <v>45505</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v>55.3</v>
+        <v>50.3</v>
       </c>
       <c r="C20" s="1">
         <f>(B20/B32-1)*100</f>
@@ -708,11 +710,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>45444</v>
+      <c r="A21" s="4" t="n">
+        <v>45474</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>62.4</v>
+        <v>55.3</v>
       </c>
       <c r="C21" s="1">
         <f>(B21/B33-1)*100</f>
@@ -720,11 +722,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="n">
-        <v>45413</v>
+      <c r="A22" s="2" t="n">
+        <v>45444</v>
       </c>
       <c r="B22" s="3" t="n">
-        <v>59.1</v>
+        <v>62.4</v>
       </c>
       <c r="C22" s="1">
         <f>(B22/B34-1)*100</f>
@@ -732,11 +734,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>45383</v>
+      <c r="A23" s="4" t="n">
+        <v>45413</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>65.7</v>
+        <v>59.1</v>
       </c>
       <c r="C23" s="1">
         <f>(B23/B35-1)*100</f>
@@ -744,11 +746,11 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="n">
-        <v>45352</v>
+      <c r="A24" s="2" t="n">
+        <v>45383</v>
       </c>
       <c r="B24" s="3" t="n">
-        <v>63</v>
+        <v>65.7</v>
       </c>
       <c r="C24" s="1">
         <f>(B24/B36-1)*100</f>
@@ -756,11 +758,11 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>45323</v>
+      <c r="A25" s="4" t="n">
+        <v>45352</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>56.3</v>
+        <v>63</v>
       </c>
       <c r="C25" s="1">
         <f>(B25/B37-1)*100</f>
@@ -768,11 +770,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="n">
-        <v>45292</v>
+      <c r="A26" s="2" t="n">
+        <v>45323</v>
       </c>
       <c r="B26" s="3" t="n">
-        <v>54.4</v>
+        <v>56.3</v>
       </c>
       <c r="C26" s="1">
         <f>(B26/B38-1)*100</f>
@@ -780,11 +782,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>45261</v>
+      <c r="A27" s="4" t="n">
+        <v>45292</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>43.7</v>
+        <v>54.4</v>
       </c>
       <c r="C27" s="1">
         <f>(B27/B39-1)*100</f>
@@ -792,11 +794,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="n">
-        <v>45231</v>
+      <c r="A28" s="2" t="n">
+        <v>45261</v>
       </c>
       <c r="B28" s="3" t="n">
-        <v>54.7</v>
+        <v>43.7</v>
       </c>
       <c r="C28" s="1">
         <f>(B28/B40-1)*100</f>
@@ -804,11 +806,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>45200</v>
+      <c r="A29" s="4" t="n">
+        <v>45231</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>53.4</v>
+        <v>54.7</v>
       </c>
       <c r="C29" s="1">
         <f>(B29/B41-1)*100</f>
@@ -816,11 +818,11 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="n">
-        <v>45170</v>
+      <c r="A30" s="2" t="n">
+        <v>45200</v>
       </c>
       <c r="B30" s="3" t="n">
-        <v>53.1</v>
+        <v>53.4</v>
       </c>
       <c r="C30" s="1">
         <f>(B30/B42-1)*100</f>
@@ -828,11 +830,11 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>45139</v>
+      <c r="A31" s="4" t="n">
+        <v>45170</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>53.5</v>
+        <v>53.1</v>
       </c>
       <c r="C31" s="1">
         <f>(B31/B43-1)*100</f>
@@ -840,11 +842,11 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="n">
-        <v>45108</v>
+      <c r="A32" s="2" t="n">
+        <v>45139</v>
       </c>
       <c r="B32" s="3" t="n">
-        <v>48.6</v>
+        <v>53.5</v>
       </c>
       <c r="C32" s="1">
         <f>(B32/B44-1)*100</f>
@@ -852,11 +854,11 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>45078</v>
+      <c r="A33" s="4" t="n">
+        <v>45108</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>50.2</v>
+        <v>48.6</v>
       </c>
       <c r="C33" s="1">
         <f>(B33/B45-1)*100</f>
@@ -864,11 +866,11 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="n">
-        <v>45047</v>
+      <c r="A34" s="2" t="n">
+        <v>45078</v>
       </c>
       <c r="B34" s="3" t="n">
-        <v>53.5</v>
+        <v>50.2</v>
       </c>
       <c r="C34" s="1">
         <f>(B34/B46-1)*100</f>
@@ -876,11 +878,11 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
-        <v>45017</v>
+      <c r="A35" s="4" t="n">
+        <v>45047</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>56.8</v>
+        <v>53.5</v>
       </c>
       <c r="C35" s="1">
         <f>(B35/B47-1)*100</f>
@@ -888,11 +890,11 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="n">
-        <v>44986</v>
+      <c r="A36" s="2" t="n">
+        <v>45017</v>
       </c>
       <c r="B36" s="3" t="n">
-        <v>58.2</v>
+        <v>56.8</v>
       </c>
       <c r="C36" s="1">
         <f>(B36/B48-1)*100</f>
@@ -900,11 +902,11 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>44958</v>
+      <c r="A37" s="4" t="n">
+        <v>44986</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>51.6</v>
+        <v>58.2</v>
       </c>
       <c r="C37" s="1">
         <f>(B37/B49-1)*100</f>
@@ -912,11 +914,11 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="n">
-        <v>44927</v>
+      <c r="A38" s="2" t="n">
+        <v>44958</v>
       </c>
       <c r="B38" s="3" t="n">
-        <v>60.1</v>
+        <v>51.6</v>
       </c>
       <c r="C38" s="1">
         <f>(B38/B50-1)*100</f>
@@ -924,11 +926,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
-        <v>44896</v>
+      <c r="A39" s="4" t="n">
+        <v>44927</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>49.3</v>
+        <v>60.1</v>
       </c>
       <c r="C39" s="1">
         <f>(B39/B51-1)*100</f>
@@ -936,11 +938,11 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="n">
-        <v>44866</v>
+      <c r="A40" s="2" t="n">
+        <v>44896</v>
       </c>
       <c r="B40" s="3" t="n">
-        <v>51.5</v>
+        <v>49.3</v>
       </c>
       <c r="C40" s="1">
         <f>(B40/B52-1)*100</f>
@@ -948,11 +950,11 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
-        <v>44835</v>
+      <c r="A41" s="4" t="n">
+        <v>44866</v>
       </c>
       <c r="B41" s="3" t="n">
-        <v>52.8</v>
+        <v>51.5</v>
       </c>
       <c r="C41" s="1">
         <f>(B41/B53-1)*100</f>
@@ -960,11 +962,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="n">
-        <v>44805</v>
+      <c r="A42" s="2" t="n">
+        <v>44835</v>
       </c>
       <c r="B42" s="3" t="n">
-        <v>52.6</v>
+        <v>52.8</v>
       </c>
       <c r="C42" s="1">
         <f>(B42/B54-1)*100</f>
@@ -972,11 +974,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
-        <v>44774</v>
+      <c r="A43" s="4" t="n">
+        <v>44805</v>
       </c>
       <c r="B43" s="3" t="n">
-        <v>53.5</v>
+        <v>52.6</v>
       </c>
       <c r="C43" s="1">
         <f>(B43/B55-1)*100</f>
@@ -984,11 +986,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="n">
-        <v>44743</v>
+      <c r="A44" s="2" t="n">
+        <v>44774</v>
       </c>
       <c r="B44" s="3" t="n">
-        <v>57</v>
+        <v>53.5</v>
       </c>
       <c r="C44" s="1">
         <f>(B44/B56-1)*100</f>
@@ -996,11 +998,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
-        <v>44713</v>
+      <c r="A45" s="4" t="n">
+        <v>44743</v>
       </c>
       <c r="B45" s="3" t="n">
-        <v>53.8</v>
+        <v>57</v>
       </c>
       <c r="C45" s="1">
         <f>(B45/B57-1)*100</f>
@@ -1008,11 +1010,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="n">
-        <v>44682</v>
+      <c r="A46" s="2" t="n">
+        <v>44713</v>
       </c>
       <c r="B46" s="3" t="n">
-        <v>61.9</v>
+        <v>53.8</v>
       </c>
       <c r="C46" s="1">
         <f>(B46/B58-1)*100</f>
@@ -1020,11 +1022,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
-        <v>44652</v>
+      <c r="A47" s="4" t="n">
+        <v>44682</v>
       </c>
       <c r="B47" s="3" t="n">
-        <v>69.90000000000001</v>
+        <v>61.9</v>
       </c>
       <c r="C47" s="1">
         <f>(B47/B59-1)*100</f>
@@ -1032,11 +1034,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="n">
-        <v>44621</v>
+      <c r="A48" s="2" t="n">
+        <v>44652</v>
       </c>
       <c r="B48" s="3" t="n">
-        <v>63</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="C48" s="1">
         <f>(B48/B60-1)*100</f>
@@ -1044,11 +1046,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
-        <v>44593</v>
+      <c r="A49" s="4" t="n">
+        <v>44621</v>
       </c>
       <c r="B49" s="3" t="n">
-        <v>63.9</v>
+        <v>63</v>
       </c>
       <c r="C49" s="1">
         <f>(B49/B61-1)*100</f>
@@ -1056,11 +1058,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="n">
-        <v>44562</v>
+      <c r="A50" s="2" t="n">
+        <v>44593</v>
       </c>
       <c r="B50" s="3" t="n">
-        <v>64.90000000000001</v>
+        <v>63.9</v>
       </c>
       <c r="C50" s="1">
         <f>(B50/B62-1)*100</f>
@@ -1068,11 +1070,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
-        <v>44531</v>
+      <c r="A51" s="4" t="n">
+        <v>44562</v>
       </c>
       <c r="B51" s="3" t="n">
-        <v>58.1</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="C51" s="1">
         <f>(B51/B63-1)*100</f>
@@ -1080,23 +1082,23 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="n">
+      <c r="A52" s="2" t="n">
+        <v>44531</v>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="C52" s="1">
+        <f>(B52/B64-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="n">
         <v>44501</v>
       </c>
-      <c r="B52" s="3" t="n">
+      <c r="B53" s="3" t="n">
         <v>61.2</v>
-      </c>
-      <c r="C52">
-        <f>(B52/B64-1)*100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="n">
-        <v>44470</v>
-      </c>
-      <c r="B53" s="3" t="n">
-        <v>63.2</v>
       </c>
       <c r="C53">
         <f>(B53/B65-1)*100</f>
@@ -1104,11 +1106,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="n">
-        <v>44440</v>
+      <c r="A54" s="2" t="n">
+        <v>44470</v>
       </c>
       <c r="B54" s="3" t="n">
-        <v>59.1</v>
+        <v>63.2</v>
       </c>
       <c r="C54">
         <f>(B54/B66-1)*100</f>
@@ -1116,11 +1118,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
-        <v>44409</v>
+      <c r="A55" s="4" t="n">
+        <v>44440</v>
       </c>
       <c r="B55" s="3" t="n">
-        <v>61.6</v>
+        <v>59.1</v>
       </c>
       <c r="C55">
         <f>(B55/B67-1)*100</f>
@@ -1128,11 +1130,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="n">
-        <v>44378</v>
+      <c r="A56" s="2" t="n">
+        <v>44409</v>
       </c>
       <c r="B56" s="3" t="n">
-        <v>63.4</v>
+        <v>61.6</v>
       </c>
       <c r="C56">
         <f>(B56/B68-1)*100</f>
@@ -1140,11 +1142,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
-        <v>44348</v>
+      <c r="A57" s="4" t="n">
+        <v>44378</v>
       </c>
       <c r="B57" s="3" t="n">
-        <v>63.8</v>
+        <v>63.4</v>
       </c>
       <c r="C57">
         <f>(B57/B69-1)*100</f>
@@ -1152,11 +1154,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="n">
-        <v>44317</v>
+      <c r="A58" s="2" t="n">
+        <v>44348</v>
       </c>
       <c r="B58" s="3" t="n">
-        <v>55.2</v>
+        <v>63.8</v>
       </c>
       <c r="C58">
         <f>(B58/B70-1)*100</f>
@@ -1164,11 +1166,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
-        <v>44287</v>
+      <c r="A59" s="4" t="n">
+        <v>44317</v>
       </c>
       <c r="B59" s="3" t="n">
-        <v>59.3</v>
+        <v>55.2</v>
       </c>
       <c r="C59">
         <f>(B59/B71-1)*100</f>
@@ -1176,11 +1178,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="n">
-        <v>44256</v>
+      <c r="A60" s="2" t="n">
+        <v>44287</v>
       </c>
       <c r="B60" s="3" t="n">
-        <v>62.1</v>
+        <v>59.3</v>
       </c>
       <c r="C60">
         <f>(B60/B72-1)*100</f>
@@ -1188,11 +1190,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
-        <v>44228</v>
+      <c r="A61" s="4" t="n">
+        <v>44256</v>
       </c>
       <c r="B61" s="3" t="n">
-        <v>66.40000000000001</v>
+        <v>62.1</v>
       </c>
       <c r="C61">
         <f>(B61/B73-1)*100</f>
@@ -1200,11 +1202,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="n">
-        <v>44197</v>
+      <c r="A62" s="2" t="n">
+        <v>44228</v>
       </c>
       <c r="B62" s="3" t="n">
-        <v>48.4</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="C62">
         <f>(B62/B74-1)*100</f>
@@ -1212,11 +1214,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
-        <v>44166</v>
+      <c r="A63" s="4" t="n">
+        <v>44197</v>
       </c>
       <c r="B63" s="3" t="n">
-        <v>46.7</v>
+        <v>48.4</v>
       </c>
       <c r="C63">
         <f>(B63/B75-1)*100</f>
@@ -1224,14 +1226,26 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="n">
-        <v>44136</v>
+      <c r="A64" s="2" t="n">
+        <v>44166</v>
       </c>
       <c r="B64" s="3" t="n">
-        <v>52.7</v>
+        <v>46.7</v>
       </c>
       <c r="C64">
         <f>(B64/B76-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>44136</v>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="C65">
+        <f>(B65/B77-1)*100</f>
         <v/>
       </c>
     </row>

--- a/data/pmi.xlsx
+++ b/data/pmi.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C65"/>
+  <dimension ref="A1:C66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.5703125" customWidth="1" min="1" max="1"/>
@@ -456,11 +456,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>61.3</v>
+        <v>59.7</v>
       </c>
       <c r="C2">
         <f>(B2/B14-1)*100</f>
@@ -470,11 +470,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>56.5</v>
+        <v>61.3</v>
       </c>
       <c r="C3">
         <f>(B3/B15-1)*100</f>
@@ -484,11 +484,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>56.3</v>
+        <v>56.5</v>
       </c>
       <c r="C4">
         <f>(B4/B16-1)*100</f>
@@ -498,11 +498,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>47</v>
+        <v>56.3</v>
       </c>
       <c r="C5">
         <f>(B5/B17-1)*100</f>
@@ -512,11 +512,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>43.3</v>
+        <v>47</v>
       </c>
       <c r="C6">
         <f>(B6/B18-1)*100</f>
@@ -526,11 +526,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>44.5</v>
+        <v>43.3</v>
       </c>
       <c r="C7">
         <f>(B7/B19-1)*100</f>
@@ -540,11 +540,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>51.7</v>
+        <v>44.5</v>
       </c>
       <c r="C8">
         <f>(B8/B20-1)*100</f>
@@ -554,11 +554,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>61.6</v>
+        <v>51.7</v>
       </c>
       <c r="C9">
         <f>(B9/B21-1)*100</f>
@@ -568,11 +568,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50</v>
+        <v>61.6</v>
       </c>
       <c r="C10">
         <f>(B10/B22-1)*100</f>
@@ -582,11 +582,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>54.6</v>
+        <v>50</v>
       </c>
       <c r="C11">
         <f>(B11/B23-1)*100</f>
@@ -596,7 +596,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -610,11 +610,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>53.8</v>
+        <v>54.6</v>
       </c>
       <c r="C13">
         <f>(B13/B25-1)*100</f>
@@ -624,11 +624,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>55.6</v>
+        <v>53.8</v>
       </c>
       <c r="C14">
         <f>(B14/B26-1)*100</f>
@@ -638,11 +638,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>53.6</v>
+        <v>55.6</v>
       </c>
       <c r="C15">
         <f>(B15/B27-1)*100</f>
@@ -650,11 +650,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>45627</v>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>44.3</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>53.6</v>
       </c>
       <c r="C16">
         <f>(B16/B28-1)*100</f>
@@ -662,23 +664,23 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="A17" s="2" t="n">
+        <v>45627</v>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="C17">
+        <f>(B17/B29-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
         <v>45597</v>
       </c>
-      <c r="B17" s="3" t="n">
+      <c r="B18" s="3" t="n">
         <v>49.7</v>
-      </c>
-      <c r="C17" s="1">
-        <f>(B17/B29-1)*100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>45566</v>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>52.2</v>
       </c>
       <c r="C18" s="1">
         <f>(B18/B30-1)*100</f>
@@ -686,11 +688,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n">
-        <v>45536</v>
+      <c r="A19" s="2" t="n">
+        <v>45566</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>54.5</v>
+        <v>52.2</v>
       </c>
       <c r="C19" s="1">
         <f>(B19/B31-1)*100</f>
@@ -698,11 +700,11 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>45505</v>
+      <c r="A20" s="4" t="n">
+        <v>45536</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v>50.3</v>
+        <v>54.5</v>
       </c>
       <c r="C20" s="1">
         <f>(B20/B32-1)*100</f>
@@ -710,11 +712,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n">
-        <v>45474</v>
+      <c r="A21" s="2" t="n">
+        <v>45505</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>55.3</v>
+        <v>50.3</v>
       </c>
       <c r="C21" s="1">
         <f>(B21/B33-1)*100</f>
@@ -722,11 +724,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>45444</v>
+      <c r="A22" s="4" t="n">
+        <v>45474</v>
       </c>
       <c r="B22" s="3" t="n">
-        <v>62.4</v>
+        <v>55.3</v>
       </c>
       <c r="C22" s="1">
         <f>(B22/B34-1)*100</f>
@@ -734,11 +736,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n">
-        <v>45413</v>
+      <c r="A23" s="2" t="n">
+        <v>45444</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>59.1</v>
+        <v>62.4</v>
       </c>
       <c r="C23" s="1">
         <f>(B23/B35-1)*100</f>
@@ -746,11 +748,11 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>45383</v>
+      <c r="A24" s="4" t="n">
+        <v>45413</v>
       </c>
       <c r="B24" s="3" t="n">
-        <v>65.7</v>
+        <v>59.1</v>
       </c>
       <c r="C24" s="1">
         <f>(B24/B36-1)*100</f>
@@ -758,11 +760,11 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="n">
-        <v>45352</v>
+      <c r="A25" s="2" t="n">
+        <v>45383</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>63</v>
+        <v>65.7</v>
       </c>
       <c r="C25" s="1">
         <f>(B25/B37-1)*100</f>
@@ -770,11 +772,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>45323</v>
+      <c r="A26" s="4" t="n">
+        <v>45352</v>
       </c>
       <c r="B26" s="3" t="n">
-        <v>56.3</v>
+        <v>63</v>
       </c>
       <c r="C26" s="1">
         <f>(B26/B38-1)*100</f>
@@ -782,11 +784,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="n">
-        <v>45292</v>
+      <c r="A27" s="2" t="n">
+        <v>45323</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>54.4</v>
+        <v>56.3</v>
       </c>
       <c r="C27" s="1">
         <f>(B27/B39-1)*100</f>
@@ -794,11 +796,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>45261</v>
+      <c r="A28" s="4" t="n">
+        <v>45292</v>
       </c>
       <c r="B28" s="3" t="n">
-        <v>43.7</v>
+        <v>54.4</v>
       </c>
       <c r="C28" s="1">
         <f>(B28/B40-1)*100</f>
@@ -806,11 +808,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="n">
-        <v>45231</v>
+      <c r="A29" s="2" t="n">
+        <v>45261</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>54.7</v>
+        <v>43.7</v>
       </c>
       <c r="C29" s="1">
         <f>(B29/B41-1)*100</f>
@@ -818,11 +820,11 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>45200</v>
+      <c r="A30" s="4" t="n">
+        <v>45231</v>
       </c>
       <c r="B30" s="3" t="n">
-        <v>53.4</v>
+        <v>54.7</v>
       </c>
       <c r="C30" s="1">
         <f>(B30/B42-1)*100</f>
@@ -830,11 +832,11 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="n">
-        <v>45170</v>
+      <c r="A31" s="2" t="n">
+        <v>45200</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>53.1</v>
+        <v>53.4</v>
       </c>
       <c r="C31" s="1">
         <f>(B31/B43-1)*100</f>
@@ -842,11 +844,11 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>45139</v>
+      <c r="A32" s="4" t="n">
+        <v>45170</v>
       </c>
       <c r="B32" s="3" t="n">
-        <v>53.5</v>
+        <v>53.1</v>
       </c>
       <c r="C32" s="1">
         <f>(B32/B44-1)*100</f>
@@ -854,11 +856,11 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="n">
-        <v>45108</v>
+      <c r="A33" s="2" t="n">
+        <v>45139</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>48.6</v>
+        <v>53.5</v>
       </c>
       <c r="C33" s="1">
         <f>(B33/B45-1)*100</f>
@@ -866,11 +868,11 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
-        <v>45078</v>
+      <c r="A34" s="4" t="n">
+        <v>45108</v>
       </c>
       <c r="B34" s="3" t="n">
-        <v>50.2</v>
+        <v>48.6</v>
       </c>
       <c r="C34" s="1">
         <f>(B34/B46-1)*100</f>
@@ -878,11 +880,11 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="n">
-        <v>45047</v>
+      <c r="A35" s="2" t="n">
+        <v>45078</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>53.5</v>
+        <v>50.2</v>
       </c>
       <c r="C35" s="1">
         <f>(B35/B47-1)*100</f>
@@ -890,11 +892,11 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
-        <v>45017</v>
+      <c r="A36" s="4" t="n">
+        <v>45047</v>
       </c>
       <c r="B36" s="3" t="n">
-        <v>56.8</v>
+        <v>53.5</v>
       </c>
       <c r="C36" s="1">
         <f>(B36/B48-1)*100</f>
@@ -902,11 +904,11 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="n">
-        <v>44986</v>
+      <c r="A37" s="2" t="n">
+        <v>45017</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>58.2</v>
+        <v>56.8</v>
       </c>
       <c r="C37" s="1">
         <f>(B37/B49-1)*100</f>
@@ -914,11 +916,11 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>44958</v>
+      <c r="A38" s="4" t="n">
+        <v>44986</v>
       </c>
       <c r="B38" s="3" t="n">
-        <v>51.6</v>
+        <v>58.2</v>
       </c>
       <c r="C38" s="1">
         <f>(B38/B50-1)*100</f>
@@ -926,11 +928,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="n">
-        <v>44927</v>
+      <c r="A39" s="2" t="n">
+        <v>44958</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>60.1</v>
+        <v>51.6</v>
       </c>
       <c r="C39" s="1">
         <f>(B39/B51-1)*100</f>
@@ -938,11 +940,11 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
-        <v>44896</v>
+      <c r="A40" s="4" t="n">
+        <v>44927</v>
       </c>
       <c r="B40" s="3" t="n">
-        <v>49.3</v>
+        <v>60.1</v>
       </c>
       <c r="C40" s="1">
         <f>(B40/B52-1)*100</f>
@@ -950,11 +952,11 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="n">
-        <v>44866</v>
+      <c r="A41" s="2" t="n">
+        <v>44896</v>
       </c>
       <c r="B41" s="3" t="n">
-        <v>51.5</v>
+        <v>49.3</v>
       </c>
       <c r="C41" s="1">
         <f>(B41/B53-1)*100</f>
@@ -962,11 +964,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
-        <v>44835</v>
+      <c r="A42" s="4" t="n">
+        <v>44866</v>
       </c>
       <c r="B42" s="3" t="n">
-        <v>52.8</v>
+        <v>51.5</v>
       </c>
       <c r="C42" s="1">
         <f>(B42/B54-1)*100</f>
@@ -974,11 +976,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="n">
-        <v>44805</v>
+      <c r="A43" s="2" t="n">
+        <v>44835</v>
       </c>
       <c r="B43" s="3" t="n">
-        <v>52.6</v>
+        <v>52.8</v>
       </c>
       <c r="C43" s="1">
         <f>(B43/B55-1)*100</f>
@@ -986,11 +988,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
-        <v>44774</v>
+      <c r="A44" s="4" t="n">
+        <v>44805</v>
       </c>
       <c r="B44" s="3" t="n">
-        <v>53.5</v>
+        <v>52.6</v>
       </c>
       <c r="C44" s="1">
         <f>(B44/B56-1)*100</f>
@@ -998,11 +1000,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="n">
-        <v>44743</v>
+      <c r="A45" s="2" t="n">
+        <v>44774</v>
       </c>
       <c r="B45" s="3" t="n">
-        <v>57</v>
+        <v>53.5</v>
       </c>
       <c r="C45" s="1">
         <f>(B45/B57-1)*100</f>
@@ -1010,11 +1012,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
-        <v>44713</v>
+      <c r="A46" s="4" t="n">
+        <v>44743</v>
       </c>
       <c r="B46" s="3" t="n">
-        <v>53.8</v>
+        <v>57</v>
       </c>
       <c r="C46" s="1">
         <f>(B46/B58-1)*100</f>
@@ -1022,11 +1024,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="n">
-        <v>44682</v>
+      <c r="A47" s="2" t="n">
+        <v>44713</v>
       </c>
       <c r="B47" s="3" t="n">
-        <v>61.9</v>
+        <v>53.8</v>
       </c>
       <c r="C47" s="1">
         <f>(B47/B59-1)*100</f>
@@ -1034,11 +1036,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
-        <v>44652</v>
+      <c r="A48" s="4" t="n">
+        <v>44682</v>
       </c>
       <c r="B48" s="3" t="n">
-        <v>69.90000000000001</v>
+        <v>61.9</v>
       </c>
       <c r="C48" s="1">
         <f>(B48/B60-1)*100</f>
@@ -1046,11 +1048,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="n">
-        <v>44621</v>
+      <c r="A49" s="2" t="n">
+        <v>44652</v>
       </c>
       <c r="B49" s="3" t="n">
-        <v>63</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="C49" s="1">
         <f>(B49/B61-1)*100</f>
@@ -1058,11 +1060,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
-        <v>44593</v>
+      <c r="A50" s="4" t="n">
+        <v>44621</v>
       </c>
       <c r="B50" s="3" t="n">
-        <v>63.9</v>
+        <v>63</v>
       </c>
       <c r="C50" s="1">
         <f>(B50/B62-1)*100</f>
@@ -1070,11 +1072,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="n">
-        <v>44562</v>
+      <c r="A51" s="2" t="n">
+        <v>44593</v>
       </c>
       <c r="B51" s="3" t="n">
-        <v>64.90000000000001</v>
+        <v>63.9</v>
       </c>
       <c r="C51" s="1">
         <f>(B51/B63-1)*100</f>
@@ -1082,11 +1084,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
-        <v>44531</v>
+      <c r="A52" s="4" t="n">
+        <v>44562</v>
       </c>
       <c r="B52" s="3" t="n">
-        <v>58.1</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="C52" s="1">
         <f>(B52/B64-1)*100</f>
@@ -1094,23 +1096,23 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="n">
+      <c r="A53" s="2" t="n">
+        <v>44531</v>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="C53" s="1">
+        <f>(B53/B65-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n">
         <v>44501</v>
       </c>
-      <c r="B53" s="3" t="n">
+      <c r="B54" s="3" t="n">
         <v>61.2</v>
-      </c>
-      <c r="C53">
-        <f>(B53/B65-1)*100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="n">
-        <v>44470</v>
-      </c>
-      <c r="B54" s="3" t="n">
-        <v>63.2</v>
       </c>
       <c r="C54">
         <f>(B54/B66-1)*100</f>
@@ -1118,11 +1120,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="n">
-        <v>44440</v>
+      <c r="A55" s="2" t="n">
+        <v>44470</v>
       </c>
       <c r="B55" s="3" t="n">
-        <v>59.1</v>
+        <v>63.2</v>
       </c>
       <c r="C55">
         <f>(B55/B67-1)*100</f>
@@ -1130,11 +1132,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
-        <v>44409</v>
+      <c r="A56" s="4" t="n">
+        <v>44440</v>
       </c>
       <c r="B56" s="3" t="n">
-        <v>61.6</v>
+        <v>59.1</v>
       </c>
       <c r="C56">
         <f>(B56/B68-1)*100</f>
@@ -1142,11 +1144,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="n">
-        <v>44378</v>
+      <c r="A57" s="2" t="n">
+        <v>44409</v>
       </c>
       <c r="B57" s="3" t="n">
-        <v>63.4</v>
+        <v>61.6</v>
       </c>
       <c r="C57">
         <f>(B57/B69-1)*100</f>
@@ -1154,11 +1156,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
-        <v>44348</v>
+      <c r="A58" s="4" t="n">
+        <v>44378</v>
       </c>
       <c r="B58" s="3" t="n">
-        <v>63.8</v>
+        <v>63.4</v>
       </c>
       <c r="C58">
         <f>(B58/B70-1)*100</f>
@@ -1166,11 +1168,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="n">
-        <v>44317</v>
+      <c r="A59" s="2" t="n">
+        <v>44348</v>
       </c>
       <c r="B59" s="3" t="n">
-        <v>55.2</v>
+        <v>63.8</v>
       </c>
       <c r="C59">
         <f>(B59/B71-1)*100</f>
@@ -1178,11 +1180,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
-        <v>44287</v>
+      <c r="A60" s="4" t="n">
+        <v>44317</v>
       </c>
       <c r="B60" s="3" t="n">
-        <v>59.3</v>
+        <v>55.2</v>
       </c>
       <c r="C60">
         <f>(B60/B72-1)*100</f>
@@ -1190,11 +1192,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="n">
-        <v>44256</v>
+      <c r="A61" s="2" t="n">
+        <v>44287</v>
       </c>
       <c r="B61" s="3" t="n">
-        <v>62.1</v>
+        <v>59.3</v>
       </c>
       <c r="C61">
         <f>(B61/B73-1)*100</f>
@@ -1202,11 +1204,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
-        <v>44228</v>
+      <c r="A62" s="4" t="n">
+        <v>44256</v>
       </c>
       <c r="B62" s="3" t="n">
-        <v>66.40000000000001</v>
+        <v>62.1</v>
       </c>
       <c r="C62">
         <f>(B62/B74-1)*100</f>
@@ -1214,11 +1216,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="n">
-        <v>44197</v>
+      <c r="A63" s="2" t="n">
+        <v>44228</v>
       </c>
       <c r="B63" s="3" t="n">
-        <v>48.4</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="C63">
         <f>(B63/B75-1)*100</f>
@@ -1226,11 +1228,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
-        <v>44166</v>
+      <c r="A64" s="4" t="n">
+        <v>44197</v>
       </c>
       <c r="B64" s="3" t="n">
-        <v>46.7</v>
+        <v>48.4</v>
       </c>
       <c r="C64">
         <f>(B64/B76-1)*100</f>
@@ -1238,14 +1240,26 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="n">
-        <v>44136</v>
+      <c r="A65" s="2" t="n">
+        <v>44166</v>
       </c>
       <c r="B65" s="3" t="n">
-        <v>52.7</v>
+        <v>46.7</v>
       </c>
       <c r="C65">
         <f>(B65/B77-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>44136</v>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="C66">
+        <f>(B66/B78-1)*100</f>
         <v/>
       </c>
     </row>
